--- a/artfynd/A 74479-2021 artfynd.xlsx
+++ b/artfynd/A 74479-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74479-2021 artfynd.xlsx
+++ b/artfynd/A 74479-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY31"/>
+  <dimension ref="A1:AY37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,59 +675,46 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3024425</v>
+        <v>101530747</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>85534</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>241</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gransotdyna</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Camarops tubulina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Shear</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Vita Hästen, Sm</t>
+          <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>544736.9415525818</v>
+        <v>544713</v>
       </c>
       <c r="R2" t="n">
-        <v>6342155.535686611</v>
+        <v>6342071</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -754,22 +741,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2007-06-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2007-06-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,58 +757,48 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>Tallskog</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Jörg Adelmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99596259</v>
+        <v>99596273</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2810</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Västlig hakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhytidiadelphus loreus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hedw.) Warnst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -843,10 +810,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>544595.2070148971</v>
+        <v>544590</v>
       </c>
       <c r="R3" t="n">
-        <v>6342168.0750331</v>
+        <v>6342163</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -876,24 +843,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -920,56 +872,46 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99594878</v>
+        <v>99615042</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>544653.2206682797</v>
+        <v>544699</v>
       </c>
       <c r="R4" t="n">
-        <v>6342321.390824752</v>
+        <v>6341960</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -996,22 +938,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1038,52 +970,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>99596785</v>
+        <v>99595048</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>544617.6791337715</v>
+        <v>544515</v>
       </c>
       <c r="R5" t="n">
-        <v>6342197.015487457</v>
+        <v>6342310</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,24 +1041,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>100-tal plantor</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,55 +1075,60 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99596533</v>
+        <v>104928318</v>
       </c>
       <c r="B6" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>Sandslät6t, Sadeshult, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>544587.9966750974</v>
+        <v>544700</v>
       </c>
       <c r="R6" t="n">
-        <v>6342182.616078188</v>
+        <v>6342210</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1229,27 +1152,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-12-03</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,68 +1182,60 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>99596409</v>
+        <v>99680539</v>
       </c>
       <c r="B7" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>4775</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>544587.1991983773</v>
+        <v>544871</v>
       </c>
       <c r="R7" t="n">
-        <v>6342156.076297943</v>
+        <v>6342127</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1352,22 +1262,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Kläckhål</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1394,56 +1299,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>99594350</v>
+        <v>99595535</v>
       </c>
       <c r="B8" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103015</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>544701.898915953</v>
+        <v>544526</v>
       </c>
       <c r="R8" t="n">
-        <v>6342334.913712523</v>
+        <v>6342277</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1473,19 +1374,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,15 +1403,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>99595048</v>
+        <v>104928316</v>
       </c>
       <c r="B9" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1528,40 +1414,49 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>upprörd, varnande</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>Sandslät6t, Sadeshult, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>544515.5468806613</v>
+        <v>544700</v>
       </c>
       <c r="R9" t="n">
-        <v>6342310.153334502</v>
+        <v>6342210</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1585,27 +1480,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-12-03</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
+          <t>2022-12-03</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1620,27 +1510,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jan Brenander, Erland Lindblad</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>99594750</v>
+        <v>3024425</v>
       </c>
       <c r="B10" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1665,19 +1550,26 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Högsby, Sm</t>
+          <t>Vita Hästen, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>544649.8544282267</v>
+        <v>544737</v>
       </c>
       <c r="R10" t="n">
-        <v>6342331.641493864</v>
+        <v>6342156</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1704,27 +1596,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2007-06-09</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
+          <t>2007-06-09</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1735,31 +1612,31 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörg Adelmann</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>99595741</v>
+        <v>99594214</v>
       </c>
       <c r="B11" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1793,10 +1670,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>544520.8447058278</v>
+        <v>544689</v>
       </c>
       <c r="R11" t="n">
-        <v>6342271.768719776</v>
+        <v>6342335</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1826,24 +1703,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>15-tal plantor</t>
+          <t>20-tal plantor</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,40 +1737,39 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>99596273</v>
+        <v>99594350</v>
       </c>
       <c r="B12" t="n">
-        <v>93054</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2810</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Västlig hakmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Rhytidiadelphus loreus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Hedw.) Warnst.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
@@ -1912,10 +1778,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>544589.8410992819</v>
+        <v>544702</v>
       </c>
       <c r="R12" t="n">
-        <v>6342162.602361854</v>
+        <v>6342335</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1945,19 +1811,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,15 +1840,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>99596626</v>
+        <v>99594447</v>
       </c>
       <c r="B13" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2019,7 +1870,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -2030,10 +1881,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>544601.0332231965</v>
+        <v>544666</v>
       </c>
       <c r="R13" t="n">
-        <v>6342181.133004867</v>
+        <v>6342343</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2063,19 +1914,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2102,15 +1943,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>99595149</v>
+        <v>99594632</v>
       </c>
       <c r="B14" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2135,11 +1971,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
@@ -2148,10 +1980,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>544505.3634987421</v>
+        <v>544665</v>
       </c>
       <c r="R14" t="n">
-        <v>6342298.673069283</v>
+        <v>6342326</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2181,19 +2013,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,15 +2047,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>99596961</v>
+        <v>99594750</v>
       </c>
       <c r="B15" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2253,11 +2075,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
@@ -2266,10 +2084,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>544707.4500658077</v>
+        <v>544650</v>
       </c>
       <c r="R15" t="n">
-        <v>6342223.437826661</v>
+        <v>6342331</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2299,19 +2117,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2338,15 +2151,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>99595525</v>
+        <v>99594878</v>
       </c>
       <c r="B16" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2371,7 +2179,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
@@ -2380,10 +2192,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>544525.668123733</v>
+        <v>544653</v>
       </c>
       <c r="R16" t="n">
-        <v>6342277.235287628</v>
+        <v>6342322</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2413,24 +2225,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2457,15 +2254,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>99595207</v>
+        <v>99595149</v>
       </c>
       <c r="B17" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2490,7 +2282,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
@@ -2499,10 +2295,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>544498.4288585642</v>
+        <v>544505</v>
       </c>
       <c r="R17" t="n">
-        <v>6342287.769365688</v>
+        <v>6342299</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2532,24 +2328,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2576,15 +2357,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>99595798</v>
+        <v>99595207</v>
       </c>
       <c r="B18" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2618,10 +2394,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>544511.7051401406</v>
+        <v>544498</v>
       </c>
       <c r="R18" t="n">
-        <v>6342264.089703714</v>
+        <v>6342288</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2651,19 +2427,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC18" t="inlineStr">
@@ -2695,15 +2461,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>99596876</v>
+        <v>99595525</v>
       </c>
       <c r="B19" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2737,10 +2498,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>544644.7665986095</v>
+        <v>544526</v>
       </c>
       <c r="R19" t="n">
-        <v>6342200.557966808</v>
+        <v>6342277</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2770,19 +2531,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC19" t="inlineStr">
@@ -2814,15 +2565,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>99594214</v>
+        <v>99595642</v>
       </c>
       <c r="B20" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2856,10 +2602,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>544688.8804514318</v>
+        <v>544511</v>
       </c>
       <c r="R20" t="n">
-        <v>6342334.772304639</v>
+        <v>6342284</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2889,24 +2635,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC20" t="inlineStr">
         <is>
-          <t>20-tal plantor</t>
+          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2933,15 +2669,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>99594632</v>
+        <v>99595741</v>
       </c>
       <c r="B21" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2975,10 +2706,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>544665.0955351981</v>
+        <v>544521</v>
       </c>
       <c r="R21" t="n">
-        <v>6342326.934023592</v>
+        <v>6342272</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -3008,24 +2739,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC21" t="inlineStr">
         <is>
-          <t>10-tal plantor</t>
+          <t>15-tal plantor</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3052,15 +2773,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>99594447</v>
+        <v>99595798</v>
       </c>
       <c r="B22" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3085,11 +2801,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
@@ -3098,10 +2810,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>544666.00999006</v>
+        <v>544512</v>
       </c>
       <c r="R22" t="n">
-        <v>6342342.645431914</v>
+        <v>6342264</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3131,19 +2843,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3170,15 +2877,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>99596711</v>
+        <v>99596259</v>
       </c>
       <c r="B23" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3212,10 +2914,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>544602.4141326082</v>
+        <v>544595</v>
       </c>
       <c r="R23" t="n">
-        <v>6342203.888823438</v>
+        <v>6342168</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3245,24 +2947,14 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>10-tal plantor</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3289,15 +2981,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>99595642</v>
+        <v>99596409</v>
       </c>
       <c r="B24" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3322,7 +3009,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
@@ -3331,10 +3022,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>544511.4884621489</v>
+        <v>544587</v>
       </c>
       <c r="R24" t="n">
-        <v>6342284.120559838</v>
+        <v>6342156</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3364,24 +3055,9 @@
           <t>2022-04-01</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2022-04-01</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3408,15 +3084,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>99608286</v>
+        <v>99596533</v>
       </c>
       <c r="B25" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3441,11 +3112,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
@@ -3454,10 +3121,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>544778.003534857</v>
+        <v>544587</v>
       </c>
       <c r="R25" t="n">
-        <v>6342171.142988674</v>
+        <v>6342183</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3484,22 +3151,17 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3526,15 +3188,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>99608189</v>
+        <v>99596626</v>
       </c>
       <c r="B26" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3559,7 +3216,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
@@ -3568,10 +3229,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>544785.3795492671</v>
+        <v>544600</v>
       </c>
       <c r="R26" t="n">
-        <v>6342141.443276326</v>
+        <v>6342181</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3598,27 +3259,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>15-tal plantor</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3645,37 +3291,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>99608298</v>
+        <v>99596711</v>
       </c>
       <c r="B27" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3687,10 +3328,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>544760.1672089028</v>
+        <v>544603</v>
       </c>
       <c r="R27" t="n">
-        <v>6342164.992961608</v>
+        <v>6342204</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3717,22 +3358,17 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2022-04-02</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>10-tal plantor</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3759,15 +3395,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>99680690</v>
+        <v>99596785</v>
       </c>
       <c r="B28" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3801,10 +3432,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>544784.955319015</v>
+        <v>544617</v>
       </c>
       <c r="R28" t="n">
-        <v>6342180.423318977</v>
+        <v>6342197</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3831,27 +3462,17 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>20-tal plantor</t>
+          <t>100-tal plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3878,53 +3499,47 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>99680539</v>
+        <v>99596876</v>
       </c>
       <c r="B29" t="n">
-        <v>4711</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100299</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>544870.1688395429</v>
+        <v>544644</v>
       </c>
       <c r="R29" t="n">
-        <v>6342127.206127599</v>
+        <v>6342200</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3951,27 +3566,17 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2022-04-05</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Kläckhål</t>
+          <t>50-tal plantor</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3998,65 +3603,54 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>104928318</v>
+        <v>99596961</v>
       </c>
       <c r="B30" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sandslät6t, Sadeshult, Sm</t>
+          <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>544700.5393499194</v>
+        <v>544707</v>
       </c>
       <c r="R30" t="n">
-        <v>6342210.368046517</v>
+        <v>6342223</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4080,22 +3674,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2022-12-03</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2022-12-03</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-04-01</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4110,77 +3694,62 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jan Brenander, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>104928316</v>
+        <v>99608189</v>
       </c>
       <c r="B31" t="n">
-        <v>56540</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>upprörd, varnande</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sandslät6t, Sadeshult, Sm</t>
+          <t>Högsby, Sm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>544700.5393499194</v>
+        <v>544785</v>
       </c>
       <c r="R31" t="n">
-        <v>6342210.368046517</v>
+        <v>6342141</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4204,22 +3773,17 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2022-12-03</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-04-02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2022-12-03</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>11:00</t>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>15-tal plantor</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4234,15 +3798,622 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jan Brenander</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jan Brenander, Erland Lindblad</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>99608286</v>
+      </c>
+      <c r="B32" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>544777</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6342171</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>99680690</v>
+      </c>
+      <c r="B33" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>544784</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6342180</v>
+      </c>
+      <c r="S33" t="n">
+        <v>25</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>20-tal plantor</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>99680765</v>
+      </c>
+      <c r="B34" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>544780</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6342207</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2022-04-05</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>99608298</v>
+      </c>
+      <c r="B35" t="n">
+        <v>106244</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221144</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Grönpyrola</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Pyrola chlorantha</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>544760</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6342165</v>
+      </c>
+      <c r="S35" t="n">
+        <v>25</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2022-04-02</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>99593281</v>
+      </c>
+      <c r="B36" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>544784</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6342209</v>
+      </c>
+      <c r="S36" t="n">
+        <v>25</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>99593725</v>
+      </c>
+      <c r="B37" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Högsby, Sm</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>544748</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6342353</v>
+      </c>
+      <c r="S37" t="n">
+        <v>25</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Högsby</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Fagerhult</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2022-04-01</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74479-2021 artfynd.xlsx
+++ b/artfynd/A 74479-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY37"/>
+  <dimension ref="A1:AZ37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101530747</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -869,6 +879,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596273</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -967,6 +982,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99615042</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1072,6 +1092,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595048</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1191,6 +1216,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104928318</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1296,6 +1326,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99680539</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595535</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1519,6 +1559,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104928316</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1630,6 +1675,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3024425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1734,6 +1784,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594214</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1837,6 +1892,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594350</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1940,6 +2000,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594447</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2044,6 +2109,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594632</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2148,6 +2218,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594750</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2251,6 +2326,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99594878</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2354,6 +2434,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595149</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2458,6 +2543,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595207</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2562,6 +2652,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595525</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2666,6 +2761,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595642</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2770,6 +2870,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595741</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2874,6 +2979,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99595798</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2978,6 +3088,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596259</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3081,6 +3196,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596409</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3185,6 +3305,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596533</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3288,6 +3413,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596626</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3392,6 +3522,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596711</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3496,6 +3631,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596785</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3600,6 +3740,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596876</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3703,6 +3848,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99596961</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3807,6 +3957,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99608189</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3910,6 +4065,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99608286</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4014,6 +4174,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99680690</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4117,6 +4282,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99680765</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4216,6 +4386,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99608298</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4315,6 +4490,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99593281</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4414,8 +4594,51 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99593725</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>